--- a/output/pdf_financials_xlsx/PGDC.xlsx
+++ b/output/pdf_financials_xlsx/PGDC.xlsx
@@ -1029,55 +1029,55 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.008495000000000001</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.015206</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.021269</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.08708299999999999</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.067708</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.049626</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.018456</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.010567</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.017841</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.016292</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.142</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>0.191</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>0.221</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>0.194</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>0.232</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>0.128</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>0</v>
+        <v>0.389</v>
       </c>
     </row>
     <row r="13">
@@ -1969,55 +1969,55 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-8.178564</v>
+        <v>-8.187059</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-2.531905</v>
+        <v>-2.547111</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-2.834674</v>
+        <v>-2.855943</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-8.19251</v>
+        <v>-8.279593</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-4.143978</v>
+        <v>-4.211686</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-2.45083</v>
+        <v>-2.500456</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-3.229683</v>
+        <v>-3.248139</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-2.466497</v>
+        <v>-2.477064</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-3.109074</v>
+        <v>-3.126915</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>1.655914</v>
+        <v>1.639622</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-10.286</v>
+        <v>-10.428</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-9.377000000000001</v>
+        <v>-9.568</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-11.443</v>
+        <v>-11.664</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-6.29</v>
+        <v>-6.484</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-8.058999999999999</v>
+        <v>-8.291</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>-11.779</v>
+        <v>-11.907</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>-8.773</v>
+        <v>-9.162000000000001</v>
       </c>
     </row>
     <row r="28">
@@ -2085,55 +2085,55 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-8.100303</v>
+        <v>-8.108798</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-2.427914</v>
+        <v>-2.44312</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-2.721177</v>
+        <v>-2.742446</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-8.080062</v>
+        <v>-8.167145</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-3.919506</v>
+        <v>-3.987214</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-2.148314</v>
+        <v>-2.19794</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-2.972941</v>
+        <v>-2.991397</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-2.378713</v>
+        <v>-2.38928</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-3.025534</v>
+        <v>-3.043375</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>2.821506</v>
+        <v>2.805214</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-9.337882</v>
+        <v>-9.479882</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-9.377000000000001</v>
+        <v>-9.568</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-9.632999999999999</v>
+        <v>-9.853999999999999</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-4.391</v>
+        <v>-4.585</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-7.561</v>
+        <v>-7.793</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-11.377</v>
+        <v>-11.505</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>-8.506</v>
+        <v>-8.895</v>
       </c>
     </row>
     <row r="30">
@@ -2193,25 +2193,25 @@
         </is>
       </c>
       <c r="L30" s="3" t="n">
-        <v>-19.68314748845935</v>
+        <v>-19.98246664277734</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>-42.74318534050506</v>
+        <v>-43.61382076761783</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>-53.20923552806009</v>
+        <v>-54.42996022978347</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>-35.58346839546191</v>
+        <v>-37.15559157212318</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>-91.98296836982969</v>
+        <v>-94.80535279805353</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>-128.8302570490318</v>
+        <v>-130.27969652361</v>
       </c>
       <c r="R30" s="3" t="n">
-        <v>-94.44814568065733</v>
+        <v>-98.76748834110593</v>
       </c>
     </row>
     <row r="31">
@@ -2385,28 +2385,28 @@
         <v>0</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.032683</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.108272</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.07814500000000001</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.66</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.291</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.231</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.185</v>
       </c>
       <c r="Q34" s="3" t="n">
         <v>0.948</v>
@@ -2501,28 +2501,28 @@
         <v>0</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.032683</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.108272</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.07814500000000001</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.66</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.291</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.231</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.185</v>
       </c>
       <c r="Q36" s="3" t="n">
         <v>0.948</v>
@@ -3197,28 +3197,28 @@
         <v>0.128716</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.03921</v>
+        <v>0.006527</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.125865</v>
+        <v>0.017593</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.146987</v>
+        <v>0.068842</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.66</v>
+        <v>0</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.6850000000000001</v>
+        <v>0</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.291</v>
+        <v>0</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.231</v>
+        <v>0</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.185</v>
+        <v>0</v>
       </c>
       <c r="Q48" s="3" t="n">
         <v>0</v>
@@ -4455,16 +4455,16 @@
         <v>3.471311</v>
       </c>
       <c r="K69" s="3" t="n">
-        <v>0</v>
+        <v>1.062428</v>
       </c>
       <c r="L69" s="3" t="n">
-        <v>0</v>
+        <v>10.102</v>
       </c>
       <c r="M69" s="3" t="n">
-        <v>0</v>
+        <v>0.334</v>
       </c>
       <c r="N69" s="3" t="n">
-        <v>0</v>
+        <v>0.517</v>
       </c>
       <c r="O69" s="3" t="n">
         <v>0.386</v>
@@ -4571,16 +4571,16 @@
         <v>3.471311</v>
       </c>
       <c r="K71" s="3" t="n">
-        <v>0</v>
+        <v>1.062428</v>
       </c>
       <c r="L71" s="3" t="n">
-        <v>0</v>
+        <v>10.102</v>
       </c>
       <c r="M71" s="3" t="n">
-        <v>0</v>
+        <v>0.334</v>
       </c>
       <c r="N71" s="3" t="n">
-        <v>0</v>
+        <v>0.517</v>
       </c>
       <c r="O71" s="3" t="n">
         <v>0.386</v>
@@ -4803,16 +4803,16 @@
         <v>1.862229</v>
       </c>
       <c r="K75" s="3" t="n">
-        <v>1.26064</v>
+        <v>0.198212</v>
       </c>
       <c r="L75" s="3" t="n">
-        <v>22.729</v>
+        <v>12.627</v>
       </c>
       <c r="M75" s="3" t="n">
-        <v>22.04</v>
+        <v>21.706</v>
       </c>
       <c r="N75" s="3" t="n">
-        <v>7.431</v>
+        <v>6.914</v>
       </c>
       <c r="O75" s="3" t="n">
         <v>9.23</v>
@@ -4916,19 +4916,19 @@
         <v>0</v>
       </c>
       <c r="J77" s="3" t="n">
-        <v>3.471311</v>
+        <v>0</v>
       </c>
       <c r="K77" s="3" t="n">
-        <v>2.431022</v>
+        <v>1.368594</v>
       </c>
       <c r="L77" s="3" t="n">
-        <v>10.776</v>
+        <v>0.674</v>
       </c>
       <c r="M77" s="3" t="n">
-        <v>0.646</v>
+        <v>0.312</v>
       </c>
       <c r="N77" s="3" t="n">
-        <v>0.772</v>
+        <v>0.255</v>
       </c>
       <c r="O77" s="3" t="n">
         <v>20.019</v>
@@ -5032,19 +5032,19 @@
         <v>0</v>
       </c>
       <c r="J79" s="3" t="n">
-        <v>3.471311</v>
+        <v>0</v>
       </c>
       <c r="K79" s="3" t="n">
-        <v>2.431022</v>
+        <v>1.368594</v>
       </c>
       <c r="L79" s="3" t="n">
-        <v>10.776</v>
+        <v>0.674</v>
       </c>
       <c r="M79" s="3" t="n">
-        <v>0.646</v>
+        <v>0.312</v>
       </c>
       <c r="N79" s="3" t="n">
-        <v>0.772</v>
+        <v>0.255</v>
       </c>
       <c r="O79" s="3" t="n">
         <v>20.019</v>
@@ -5104,7 +5104,7 @@
         </is>
       </c>
       <c r="J80" s="3" t="n">
-        <v>-2.090069656725827</v>
+        <v>-1.045034828362913</v>
       </c>
       <c r="K80" s="3" t="n">
         <v>-1.573822346780297</v>
@@ -5394,19 +5394,19 @@
         <v>0.25</v>
       </c>
       <c r="J85" s="3" t="n">
-        <v>0</v>
+        <v>0.971695</v>
       </c>
       <c r="K85" s="3" t="n">
-        <v>0</v>
+        <v>0.773436</v>
       </c>
       <c r="L85" s="3" t="n">
-        <v>0</v>
+        <v>0.631</v>
       </c>
       <c r="M85" s="3" t="n">
-        <v>14.242</v>
+        <v>14.576</v>
       </c>
       <c r="N85" s="3" t="n">
-        <v>21.186</v>
+        <v>21.703</v>
       </c>
       <c r="O85" s="3" t="n">
         <v>4.069</v>
@@ -12233,7 +12233,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -15664,7 +15664,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -17078,7 +17078,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LongTermDebt</t>
+          <t>CurrentDebt</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -17688,7 +17688,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -19330,7 +19330,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LongTermDebt</t>
+          <t>CurrentDebt</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -21172,7 +21172,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -22663,7 +22663,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>LongTermDebt</t>
+          <t>CurrentDebt</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -24863,7 +24863,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -74511,7 +74511,7 @@
       </c>
       <c r="D658" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E658" t="inlineStr">
@@ -74709,7 +74709,7 @@
       </c>
       <c r="D660" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E660" t="inlineStr">
@@ -80451,7 +80451,7 @@
       </c>
       <c r="D718" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E718" t="inlineStr">
@@ -81568,7 +81568,7 @@
       </c>
       <c r="D729" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E729" t="inlineStr">
@@ -83293,7 +83293,7 @@
       </c>
       <c r="D746" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E746" t="inlineStr">
@@ -83499,7 +83499,7 @@
       </c>
       <c r="D748" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E748" t="inlineStr">
@@ -86768,7 +86768,7 @@
       </c>
       <c r="D781" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E781" t="inlineStr">
@@ -87259,7 +87259,7 @@
       </c>
       <c r="D786" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E786" t="inlineStr">
@@ -91350,7 +91350,7 @@
       </c>
       <c r="D827" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E827" t="inlineStr">
@@ -98686,7 +98686,7 @@
       </c>
       <c r="D901" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E901" t="inlineStr">
@@ -101696,7 +101696,7 @@
       </c>
       <c r="D931" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E931" s="5" t="n">

--- a/output/pdf_financials_xlsx/PGDC.xlsx
+++ b/output/pdf_financials_xlsx/PGDC.xlsx
@@ -2057,10 +2057,10 @@
         <v>1.165592</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>0.948118</v>
+        <v>4.512</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>0</v>
+        <v>1.844</v>
       </c>
       <c r="N28" s="3" t="n">
         <v>1.81</v>
@@ -2115,10 +2115,10 @@
         <v>2.805214</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-9.479882</v>
+        <v>-5.916</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-9.568</v>
+        <v>-7.724</v>
       </c>
       <c r="N29" s="3" t="n">
         <v>-9.853999999999999</v>
@@ -2193,10 +2193,10 @@
         </is>
       </c>
       <c r="L30" s="3" t="n">
-        <v>-19.98246664277734</v>
+        <v>-12.47022617567083</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>-43.61382076761783</v>
+        <v>-35.20831434041389</v>
       </c>
       <c r="N30" s="3" t="n">
         <v>-54.42996022978347</v>
@@ -6223,25 +6223,25 @@
         <v>0</v>
       </c>
       <c r="L100" s="3" t="n">
-        <v>0</v>
+        <v>4.512</v>
       </c>
       <c r="M100" s="3" t="n">
-        <v>0</v>
+        <v>1.844</v>
       </c>
       <c r="N100" s="3" t="n">
-        <v>0</v>
+        <v>2.346</v>
       </c>
       <c r="O100" s="3" t="n">
-        <v>0</v>
+        <v>1.735</v>
       </c>
       <c r="P100" s="3" t="n">
-        <v>0</v>
+        <v>1.516</v>
       </c>
       <c r="Q100" s="3" t="n">
-        <v>0</v>
+        <v>1.408</v>
       </c>
       <c r="R100" s="3" t="n">
-        <v>0</v>
+        <v>1.685</v>
       </c>
     </row>
     <row r="101">
@@ -6901,7 +6901,7 @@
         <v>0</v>
       </c>
       <c r="F112" s="3" t="n">
-        <v>0</v>
+        <v>0.057201</v>
       </c>
       <c r="G112" s="3" t="n">
         <v>0</v>
@@ -6919,25 +6919,25 @@
         <v>0</v>
       </c>
       <c r="L112" s="3" t="n">
-        <v>0</v>
+        <v>7.515</v>
       </c>
       <c r="M112" s="3" t="n">
-        <v>0</v>
+        <v>0.113</v>
       </c>
       <c r="N112" s="3" t="n">
-        <v>0</v>
+        <v>0.337</v>
       </c>
       <c r="O112" s="3" t="n">
-        <v>0</v>
+        <v>0.024</v>
       </c>
       <c r="P112" s="3" t="n">
-        <v>0</v>
+        <v>0.16</v>
       </c>
       <c r="Q112" s="3" t="n">
-        <v>0</v>
+        <v>0.039</v>
       </c>
       <c r="R112" s="3" t="n">
-        <v>0</v>
+        <v>0.111</v>
       </c>
     </row>
     <row r="113">
@@ -45267,7 +45267,11 @@
           <t>Depreciation of property, plant and equipment 11</t>
         </is>
       </c>
-      <c r="D364" t="inlineStr"/>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E364" t="inlineStr">
         <is>
           <t>-</t>
@@ -47058,7 +47062,11 @@
           <t>Proceeds from disposal of property, plant and equipment 11</t>
         </is>
       </c>
-      <c r="D383" t="inlineStr"/>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E383" t="inlineStr">
         <is>
           <t>-</t>
@@ -52236,7 +52244,11 @@
           <t>Depreciation of property, plant and equipment 22</t>
         </is>
       </c>
-      <c r="D435" t="inlineStr"/>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E435" t="inlineStr">
         <is>
           <t>-</t>
@@ -54030,7 +54042,11 @@
           <t>Proceeds from disposal of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D453" t="inlineStr"/>
+      <c r="D453" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E453" t="inlineStr">
         <is>
           <t>-</t>
@@ -66079,7 +66095,11 @@
           <t>Proceeds on sale of property and equipment</t>
         </is>
       </c>
-      <c r="D574" t="inlineStr"/>
+      <c r="D574" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E574" t="inlineStr">
         <is>
           <t>-</t>
@@ -67487,7 +67507,11 @@
           <t>Proceeds on sale of property and equipment 8</t>
         </is>
       </c>
-      <c r="D588" t="inlineStr"/>
+      <c r="D588" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E588" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/PGDC.xlsx
+++ b/output/pdf_financials_xlsx/PGDC.xlsx
@@ -739,37 +739,37 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0</v>
+        <v>0.198364</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0</v>
+        <v>0.244622</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0</v>
+        <v>0.656272</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0</v>
+        <v>1.005061</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0</v>
+        <v>1.121605</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0</v>
+        <v>0.684156</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>0</v>
+        <v>0.294781</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>0</v>
+        <v>0.349651</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0</v>
+        <v>0.319896</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0</v>
+        <v>0.299855</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0</v>
+        <v>0.122904</v>
       </c>
       <c r="M7" s="3" t="n">
         <v>0</v>
@@ -2736,7 +2736,7 @@
         <v>0</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>0</v>
+        <v>0.126453</v>
       </c>
       <c r="K40" s="3" t="n">
         <v>0</v>
@@ -2794,7 +2794,7 @@
         <v>0.085982</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>0.126453</v>
+        <v>0.252906</v>
       </c>
       <c r="K41" s="3" t="n">
         <v>2.14483</v>
@@ -3200,7 +3200,7 @@
         <v>0.006527</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.017593</v>
+        <v>0</v>
       </c>
       <c r="K48" s="3" t="n">
         <v>0.068842</v>
@@ -4162,13 +4162,13 @@
         <v>0</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>0</v>
+        <v>1.103094</v>
       </c>
       <c r="K64" s="3" t="n">
-        <v>0</v>
+        <v>2.262425</v>
       </c>
       <c r="L64" s="3" t="n">
-        <v>0</v>
+        <v>1.912306</v>
       </c>
       <c r="M64" s="3" t="n">
         <v>0</v>
@@ -6629,25 +6629,25 @@
         <v>0.034528</v>
       </c>
       <c r="L107" s="3" t="n">
-        <v>0</v>
+        <v>0.19</v>
       </c>
       <c r="M107" s="3" t="n">
-        <v>0</v>
+        <v>0.127</v>
       </c>
       <c r="N107" s="3" t="n">
-        <v>0</v>
+        <v>0.362</v>
       </c>
       <c r="O107" s="3" t="n">
-        <v>0</v>
+        <v>0.349</v>
       </c>
       <c r="P107" s="3" t="n">
-        <v>0</v>
+        <v>0.135</v>
       </c>
       <c r="Q107" s="3" t="n">
-        <v>0</v>
+        <v>0.012</v>
       </c>
       <c r="R107" s="3" t="n">
-        <v>0</v>
+        <v>0.406</v>
       </c>
     </row>
     <row r="108">
@@ -6797,31 +6797,31 @@
         <v>0</v>
       </c>
       <c r="J110" s="3" t="n">
-        <v>0</v>
+        <v>0.043663</v>
       </c>
       <c r="K110" s="3" t="n">
-        <v>0</v>
+        <v>0.068068</v>
       </c>
       <c r="L110" s="3" t="n">
-        <v>0</v>
+        <v>0.578</v>
       </c>
       <c r="M110" s="3" t="n">
-        <v>0</v>
+        <v>0.179</v>
       </c>
       <c r="N110" s="3" t="n">
-        <v>0</v>
+        <v>0.066</v>
       </c>
       <c r="O110" s="3" t="n">
-        <v>0</v>
+        <v>0.305</v>
       </c>
       <c r="P110" s="3" t="n">
-        <v>0</v>
+        <v>0.282</v>
       </c>
       <c r="Q110" s="3" t="n">
-        <v>0</v>
+        <v>0.121</v>
       </c>
       <c r="R110" s="3" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="111">
@@ -7020,13 +7020,13 @@
         <v>0</v>
       </c>
       <c r="G114" s="3" t="n">
-        <v>0</v>
+        <v>-0.358799</v>
       </c>
       <c r="H114" s="3" t="n">
-        <v>0</v>
+        <v>-1.745182</v>
       </c>
       <c r="I114" s="3" t="n">
-        <v>0</v>
+        <v>-0.475113</v>
       </c>
       <c r="J114" s="3" t="n">
         <v>0</v>
@@ -45550,7 +45550,11 @@
           <t>Share based payment expense 19</t>
         </is>
       </c>
-      <c r="D367" t="inlineStr"/>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E367" t="inlineStr">
         <is>
           <t>-</t>
@@ -46037,7 +46041,11 @@
           <t>Accretion expense 8</t>
         </is>
       </c>
-      <c r="D372" t="inlineStr"/>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E372" t="inlineStr">
         <is>
           <t>-</t>
@@ -50236,7 +50244,11 @@
           <t>Share based payment expense 18</t>
         </is>
       </c>
-      <c r="D415" t="inlineStr"/>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E415" t="inlineStr">
         <is>
           <t>-</t>
@@ -50634,7 +50646,11 @@
           <t>Accretion expense 8</t>
         </is>
       </c>
-      <c r="D419" t="inlineStr"/>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E419" t="inlineStr">
         <is>
           <t>-</t>
@@ -51440,7 +51456,11 @@
           <t>Accretion expense 8</t>
         </is>
       </c>
-      <c r="D427" t="inlineStr"/>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E427" t="inlineStr">
         <is>
           <t>-</t>
@@ -52145,7 +52165,11 @@
           <t>Net Income/(Loss) $</t>
         </is>
       </c>
-      <c r="D434" t="inlineStr"/>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E434" t="inlineStr">
         <is>
           <t>-</t>
@@ -52446,7 +52470,11 @@
           <t>Share based payment expense 20</t>
         </is>
       </c>
-      <c r="D437" t="inlineStr"/>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E437" t="inlineStr">
         <is>
           <t>-</t>
@@ -52842,7 +52870,11 @@
           <t>Accretion expense 9</t>
         </is>
       </c>
-      <c r="D441" t="inlineStr"/>
+      <c r="D441" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E441" t="inlineStr">
         <is>
           <t>-</t>
@@ -55468,7 +55500,11 @@
           <t>Net income (loss) $</t>
         </is>
       </c>
-      <c r="D467" t="inlineStr"/>
+      <c r="D467" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E467" t="inlineStr">
         <is>
           <t>-</t>
@@ -55971,7 +56007,11 @@
           <t>Accretion 9</t>
         </is>
       </c>
-      <c r="D472" t="inlineStr"/>
+      <c r="D472" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E472" t="inlineStr">
         <is>
           <t>-</t>
@@ -60367,7 +60407,11 @@
           <t>Accretion</t>
         </is>
       </c>
-      <c r="D516" t="inlineStr"/>
+      <c r="D516" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E516" t="inlineStr">
         <is>
           <t>-</t>
@@ -61161,7 +61205,11 @@
           <t>Purchase of marketable securities</t>
         </is>
       </c>
-      <c r="D524" t="inlineStr"/>
+      <c r="D524" t="inlineStr">
+        <is>
+          <t>PurchaseOfInvestment</t>
+        </is>
+      </c>
       <c r="E524" t="inlineStr">
         <is>
           <t>-</t>
@@ -63151,7 +63199,11 @@
           <t>Purchases of marketable securities</t>
         </is>
       </c>
-      <c r="D544" t="inlineStr"/>
+      <c r="D544" t="inlineStr">
+        <is>
+          <t>PurchaseOfInvestment</t>
+        </is>
+      </c>
       <c r="E544" t="inlineStr">
         <is>
           <t>-</t>
@@ -64319,7 +64371,11 @@
           <t>Deferred tax recovery</t>
         </is>
       </c>
-      <c r="D556" t="inlineStr"/>
+      <c r="D556" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E556" t="inlineStr">
         <is>
           <t>-</t>
@@ -70121,7 +70177,11 @@
           <t>Future income taxes</t>
         </is>
       </c>
-      <c r="D614" t="inlineStr"/>
+      <c r="D614" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E614" t="inlineStr">
         <is>
           <t>-</t>
@@ -71844,7 +71904,11 @@
           <t>Future income tax recovery (Note 8)</t>
         </is>
       </c>
-      <c r="D631" t="inlineStr"/>
+      <c r="D631" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E631" t="inlineStr">
         <is>
           <t>-</t>
@@ -86242,7 +86306,11 @@
           <t>Directors fees</t>
         </is>
       </c>
-      <c r="D775" t="inlineStr"/>
+      <c r="D775" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E775" t="inlineStr">
         <is>
           <t>-</t>
@@ -86497,7 +86565,11 @@
           <t>Administrative and office expenses 16</t>
         </is>
       </c>
-      <c r="D778" t="inlineStr"/>
+      <c r="D778" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E778" t="inlineStr">
         <is>
           <t>-</t>
@@ -91075,7 +91147,11 @@
           <t>Administrative and office expenses 14</t>
         </is>
       </c>
-      <c r="D824" t="inlineStr"/>
+      <c r="D824" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E824" t="inlineStr">
         <is>
           <t>-</t>
@@ -93649,7 +93725,11 @@
           <t>Administrative and office expenses</t>
         </is>
       </c>
-      <c r="D850" t="inlineStr"/>
+      <c r="D850" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E850" s="5" t="n">
         <v>0.198364</v>
       </c>
@@ -102518,7 +102598,11 @@
           <t>Future income tax recovery (Note 8)</t>
         </is>
       </c>
-      <c r="D939" t="inlineStr"/>
+      <c r="D939" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E939" t="inlineStr">
         <is>
           <t>-</t>
